--- a/exports/gym_members.xlsx
+++ b/exports/gym_members.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,100 +419,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Member ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Expiry Date</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Payment Status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Membership Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>asdf</t>
+          <t>pandhare</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12345678</t>
+          <t>7799986754</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Half-Yearly</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-12-1</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2027-12-01</t>
+          <t>2027-05-11</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Paid</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>satya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9864647372</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Half-Yearly</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-12-12</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2027-06-12</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
